--- a/data/trans_dic/P62A$jubilacion-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P62A$jubilacion-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de jubilación</t>
+          <t>Población que, al menos, percibe una pensión de jubilación (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,23</t>
+          <t>0,0; 73,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,21</t>
+          <t>0,0; 41,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,04</t>
+          <t>0,0; 31,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,18</t>
+          <t>0,0; 25,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,49; 55,22</t>
+          <t>15,0; 53,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,27</t>
+          <t>0,0; 8,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,64</t>
+          <t>0,0; 12,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 36,29</t>
+          <t>4,7; 36,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 23,38</t>
+          <t>2,83; 24,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,0</t>
+          <t>0,0; 14,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,4; 39,97</t>
+          <t>13,18; 40,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,58</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 15,26</t>
+          <t>1,53; 14,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,71</t>
+          <t>0,0; 8,54</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,05; 54,41</t>
+          <t>25,42; 54,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 17,57</t>
+          <t>2,93; 16,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,61; 45,46</t>
+          <t>23,84; 45,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 28,08</t>
+          <t>6,76; 27,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,44; 43,57</t>
+          <t>16,43; 43,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 15,22</t>
+          <t>1,82; 14,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,7; 38,76</t>
+          <t>13,12; 37,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 15,69</t>
+          <t>1,93; 16,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,64; 45,1</t>
+          <t>24,32; 44,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 13,21</t>
+          <t>3,65; 12,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22,25; 39,48</t>
+          <t>22,59; 39,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,78; 20,38</t>
+          <t>6,13; 19,49</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,86; 88,12</t>
+          <t>76,95; 88,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,42; 72,0</t>
+          <t>56,7; 71,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,56; 82,05</t>
+          <t>70,3; 82,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,6; 44,04</t>
+          <t>28,8; 43,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,53; 44,45</t>
+          <t>23,51; 45,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,6; 34,96</t>
+          <t>16,63; 35,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,92; 52,71</t>
+          <t>33,31; 52,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,46; 24,95</t>
+          <t>14,35; 25,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61,31; 72,95</t>
+          <t>61,25; 72,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44,5; 57,14</t>
+          <t>43,65; 56,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,01; 70,26</t>
+          <t>59,07; 70,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,83; 35,08</t>
+          <t>25,26; 35,16</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>97,44; 99,69</t>
+          <t>97,15; 99,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>94,67; 99,29</t>
+          <t>94,62; 99,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97,78; 100,0</t>
+          <t>97,74; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57,39; 66,05</t>
+          <t>57,49; 66,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,37; 56,24</t>
+          <t>41,73; 56,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50,59; 63,34</t>
+          <t>50,66; 63,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54,64; 67,79</t>
+          <t>54,03; 67,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50,77; 91,37</t>
+          <t>51,34; 92,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76,38; 83,35</t>
+          <t>76,27; 83,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76,75; 83,94</t>
+          <t>76,94; 83,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79,76; 86,16</t>
+          <t>79,6; 86,38</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>57,02; 88,39</t>
+          <t>57,01; 86,72</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>99,12; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>97,92; 100,0</t>
+          <t>98,12; 100,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97,08; 99,64</t>
+          <t>96,79; 99,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61,05; 70,36</t>
+          <t>60,82; 70,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,03; 45,93</t>
+          <t>32,69; 45,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,0; 42,98</t>
+          <t>31,72; 42,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,18; 45,85</t>
+          <t>32,82; 45,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24,24; 31,48</t>
+          <t>24,19; 31,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>62,15; 71,38</t>
+          <t>61,66; 71,3</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60,9; 69,57</t>
+          <t>61,24; 69,52</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62,68; 71,0</t>
+          <t>62,52; 71,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,22; 47,61</t>
+          <t>41,34; 47,53</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>86,54; 91,23</t>
+          <t>86,53; 91,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>73,16; 79,17</t>
+          <t>73,13; 79,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80,8; 86,13</t>
+          <t>80,6; 85,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49,18; 55,22</t>
+          <t>49,34; 55,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,09; 43,06</t>
+          <t>34,92; 42,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,81; 39,39</t>
+          <t>32,15; 39,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,38; 47,21</t>
+          <t>39,12; 47,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>30,59; 72,56</t>
+          <t>30,52; 71,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>64,44; 69,68</t>
+          <t>64,47; 69,62</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55,07; 60,04</t>
+          <t>54,9; 60,06</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63,01; 67,74</t>
+          <t>62,79; 67,48</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,78; 65,94</t>
+          <t>41,72; 66,3</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de jubilación</t>
+          <t>Población que, al menos, percibe una pensión de jubilación (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 715</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1425</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1625</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1535</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 762</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1813</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1666</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1860</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1091</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 1836</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1787</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2335</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3827</t>
+          <t>0; 3852</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1867</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5229</t>
+          <t>0; 5989</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2146</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1841</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1733</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1749</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4488</t>
+          <t>0; 4981</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5507</t>
+          <t>0; 6997</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3634; 13844</t>
+          <t>3762; 13345</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4330</t>
+          <t>0; 4171</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4617</t>
+          <t>0; 3808</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1985</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>916; 7000</t>
+          <t>907; 6989</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2163</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>826; 6698</t>
+          <t>811; 7145</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3361</t>
+          <t>0; 3784</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5502; 17729</t>
+          <t>5846; 17828</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4821</t>
+          <t>0; 5159</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>918; 8877</t>
+          <t>887; 8341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3066</t>
+          <t>0; 3906</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11928; 24918</t>
+          <t>11643; 24912</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3099; 13323</t>
+          <t>2218; 12592</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18612; 35831</t>
+          <t>18794; 36195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3212; 15328</t>
+          <t>3689; 15147</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6749; 17888</t>
+          <t>6748; 17914</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1000; 8317</t>
+          <t>992; 7988</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6013; 18350</t>
+          <t>6209; 17933</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>770; 6269</t>
+          <t>770; 6589</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22269; 39173</t>
+          <t>21127; 38668</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5156; 17229</t>
+          <t>4765; 16668</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28074; 49809</t>
+          <t>28494; 49314</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5464; 19265</t>
+          <t>5799; 18427</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>129739; 148756</t>
+          <t>129902; 148916</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>97845; 124862</t>
+          <t>98327; 124739</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>139329; 164348</t>
+          <t>140822; 165245</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50386; 74953</t>
+          <t>49022; 73621</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18810; 35526</t>
+          <t>18794; 35972</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15897; 33472</t>
+          <t>15928; 33981</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36539; 58501</t>
+          <t>36972; 58232</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14294; 26501</t>
+          <t>15240; 26699</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>152496; 181460</t>
+          <t>152343; 181262</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>119791; 153804</t>
+          <t>117506; 152807</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>183698; 218706</t>
+          <t>183891; 218805</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>68628; 96969</t>
+          <t>69822; 97180</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>278375; 284787</t>
+          <t>277542; 284796</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>289372; 303510</t>
+          <t>289216; 303404</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>316096; 323265</t>
+          <t>315948; 323265</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>171894; 197838</t>
+          <t>172178; 198080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>73117; 99405</t>
+          <t>73757; 99021</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>114122; 142892</t>
+          <t>114273; 143513</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>127889; 158673</t>
+          <t>126466; 157144</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>218969; 394065</t>
+          <t>221401; 399353</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>353173; 385435</t>
+          <t>352669; 385274</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>407711; 445958</t>
+          <t>408724; 445090</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>444538; 480183</t>
+          <t>443640; 481414</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>416696; 645964</t>
+          <t>416629; 633700</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>204553; 206378</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>243627; 248789</t>
+          <t>244122; 248789</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>243086; 249508</t>
+          <t>242351; 249509</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150894; 173915</t>
+          <t>150315; 173371</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>81683; 113594</t>
+          <t>80833; 113591</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>94853; 127422</t>
+          <t>94034; 127001</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94144; 134118</t>
+          <t>96000; 132911</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>77319; 100425</t>
+          <t>77170; 99799</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>281944; 323844</t>
+          <t>279719; 323479</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>332028; 379290</t>
+          <t>333912; 379041</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>340322; 385481</t>
+          <t>339461; 388587</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>233385; 269551</t>
+          <t>234072; 269132</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>638560; 673151</t>
+          <t>638499; 672924</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>637330; 689653</t>
+          <t>637078; 692109</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>728215; 776258</t>
+          <t>726361; 774060</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>394198; 442602</t>
+          <t>395485; 444252</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>202158; 248046</t>
+          <t>201156; 247086</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>237356; 293882</t>
+          <t>239895; 295315</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>290214; 347978</t>
+          <t>288316; 346981</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>286820; 680323</t>
+          <t>286160; 674187</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>846704; 915506</t>
+          <t>847160; 914828</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>890632; 970909</t>
+          <t>887821; 971263</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1032356; 1109783</t>
+          <t>1028731; 1105522</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>726665; 1146732</t>
+          <t>725456; 1152980</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$jubilacion-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P62A$jubilacion-Edad-trans_dic.xlsx
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,7</t>
+          <t>0,0; 77,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,48</t>
+          <t>0,0; 37,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,12</t>
+          <t>0,0; 32,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,64</t>
+          <t>0,0; 22,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -997,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,0; 53,23</t>
+          <t>15,05; 56,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,93</t>
+          <t>0,0; 8,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,9</t>
+          <t>0,0; 19,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 36,24</t>
+          <t>4,8; 35,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,32 +1027,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 24,94</t>
+          <t>2,87; 21,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,64</t>
+          <t>0,0; 13,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,18; 40,19</t>
+          <t>13,27; 42,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,97</t>
+          <t>0,0; 6,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,34</t>
+          <t>1,51; 13,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,54</t>
+          <t>0,0; 8,1</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,42; 54,4</t>
+          <t>26,79; 55,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 16,61</t>
+          <t>4,04; 17,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,84; 45,92</t>
+          <t>22,82; 45,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 27,74</t>
+          <t>6,42; 27,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,43; 43,63</t>
+          <t>16,46; 44,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 14,62</t>
+          <t>1,78; 15,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,12; 37,88</t>
+          <t>12,64; 37,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 16,49</t>
+          <t>1,66; 14,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,32; 44,52</t>
+          <t>25,46; 45,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 12,78</t>
+          <t>3,88; 13,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22,59; 39,09</t>
+          <t>21,08; 39,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,13; 19,49</t>
+          <t>5,13; 17,91</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,95; 88,22</t>
+          <t>77,69; 88,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,7; 71,93</t>
+          <t>56,85; 72,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70,3; 82,5</t>
+          <t>70,72; 82,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,8; 43,25</t>
+          <t>29,24; 41,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,51; 45,01</t>
+          <t>24,46; 44,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,63; 35,49</t>
+          <t>17,22; 34,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,31; 52,46</t>
+          <t>33,14; 52,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,35; 25,14</t>
+          <t>14,32; 25,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61,25; 72,87</t>
+          <t>61,69; 73,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43,65; 56,77</t>
+          <t>44,13; 56,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,07; 70,29</t>
+          <t>59,08; 70,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,26; 35,16</t>
+          <t>24,84; 34,84</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>58,32%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>97,15; 99,69</t>
+          <t>97,34; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>94,62; 99,26</t>
+          <t>94,72; 99,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97,74; 100,0</t>
+          <t>97,75; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57,49; 66,13</t>
+          <t>57,07; 66,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,73; 56,03</t>
+          <t>41,64; 56,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50,66; 63,62</t>
+          <t>50,41; 63,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54,03; 67,14</t>
+          <t>53,5; 67,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,34; 92,6</t>
+          <t>49,22; 58,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76,27; 83,32</t>
+          <t>76,18; 83,71</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76,94; 83,78</t>
+          <t>76,63; 83,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79,6; 86,38</t>
+          <t>79,72; 86,48</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>57,01; 86,72</t>
+          <t>55,0; 61,35</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -1562,57 +1562,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>98,12; 100,0</t>
+          <t>97,88; 100,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96,79; 99,64</t>
+          <t>97,14; 99,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60,82; 70,14</t>
+          <t>61,14; 70,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,69; 45,93</t>
+          <t>32,82; 45,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,72; 42,84</t>
+          <t>31,21; 42,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,82; 45,43</t>
+          <t>32,56; 45,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24,19; 31,28</t>
+          <t>24,66; 31,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61,66; 71,3</t>
+          <t>62,2; 71,61</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61,24; 69,52</t>
+          <t>61,02; 69,76</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62,52; 71,57</t>
+          <t>62,07; 71,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,34; 47,53</t>
+          <t>41,49; 47,84</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>86,53; 91,2</t>
+          <t>86,66; 91,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>73,13; 79,45</t>
+          <t>73,21; 79,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80,6; 85,89</t>
+          <t>81,03; 86,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49,34; 55,43</t>
+          <t>49,2; 55,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,92; 42,89</t>
+          <t>35,11; 43,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,15; 39,58</t>
+          <t>32,34; 39,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,12; 47,08</t>
+          <t>39,17; 47,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>30,52; 71,91</t>
+          <t>29,69; 34,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>64,47; 69,62</t>
+          <t>64,7; 69,99</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54,9; 60,06</t>
+          <t>54,96; 60,06</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62,79; 67,48</t>
+          <t>63,1; 67,69</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,72; 66,3</t>
+          <t>40,72; 44,61</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3852</t>
+          <t>0; 4046</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5989</t>
+          <t>0; 5348</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4981</t>
+          <t>0; 5257</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6997</t>
+          <t>0; 6226</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>746</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>746</t>
         </is>
       </c>
     </row>
@@ -2484,17 +2484,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3762; 13345</t>
+          <t>3773; 14220</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4171</t>
+          <t>0; 3958</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3808</t>
+          <t>0; 5617</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>907; 6989</t>
+          <t>926; 6918</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2514,32 +2514,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>811; 7145</t>
+          <t>821; 6268</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3784</t>
+          <t>0; 3736</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5846; 17828</t>
+          <t>5886; 18812</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5159</t>
+          <t>0; 5250</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>887; 8341</t>
+          <t>878; 7938</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3906</t>
+          <t>0; 3951</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>11457</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11643; 24912</t>
+          <t>12267; 25344</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2218; 12592</t>
+          <t>3061; 13374</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18794; 36195</t>
+          <t>17987; 36050</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3689; 15147</t>
+          <t>3895; 16734</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6748; 17914</t>
+          <t>6758; 18452</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>992; 7988</t>
+          <t>974; 8630</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6209; 17933</t>
+          <t>5982; 17602</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>770; 6589</t>
+          <t>743; 6608</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21127; 38668</t>
+          <t>22115; 39466</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4765; 16668</t>
+          <t>5059; 18038</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28494; 49314</t>
+          <t>26590; 49514</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5799; 18427</t>
+          <t>5408; 18884</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61812</t>
+          <t>64865</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20246</t>
+          <t>22656</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82058</t>
+          <t>87521</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>129902; 148916</t>
+          <t>131142; 149204</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>98327; 124739</t>
+          <t>98592; 125659</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>140822; 165245</t>
+          <t>141658; 165247</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49022; 73621</t>
+          <t>52498; 75051</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18794; 35972</t>
+          <t>19548; 35250</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15928; 33981</t>
+          <t>16489; 32646</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36972; 58232</t>
+          <t>36785; 57912</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15240; 26699</t>
+          <t>16812; 30325</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>152343; 181262</t>
+          <t>153438; 181573</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>117506; 152807</t>
+          <t>118798; 152770</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>183891; 218805</t>
+          <t>183914; 220302</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>69822; 97180</t>
+          <t>73762; 103460</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185644</t>
+          <t>205425</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>324154</t>
+          <t>133108</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>509798</t>
+          <t>338533</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>277542; 284796</t>
+          <t>278067; 285674</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>289216; 303404</t>
+          <t>289524; 303486</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>315948; 323265</t>
+          <t>315991; 323265</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>172178; 198080</t>
+          <t>189228; 219238</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>73757; 99021</t>
+          <t>73601; 98966</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>114273; 143513</t>
+          <t>113721; 143119</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>126466; 157144</t>
+          <t>125210; 156934</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>221401; 399353</t>
+          <t>122490; 145072</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>352669; 385274</t>
+          <t>352256; 387105</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>408724; 445090</t>
+          <t>407105; 444515</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>443640; 481414</t>
+          <t>444304; 481959</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>416629; 633700</t>
+          <t>319279; 356097</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>162416</t>
+          <t>178598</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>88341</t>
+          <t>98463</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>250757</t>
+          <t>277061</t>
         </is>
       </c>
     </row>
@@ -3321,57 +3321,57 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>244122; 248789</t>
+          <t>243521; 248789</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>242351; 249509</t>
+          <t>243243; 249509</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150315; 173371</t>
+          <t>166109; 190785</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>80833; 113591</t>
+          <t>81160; 112294</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>94034; 127001</t>
+          <t>92533; 126109</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96000; 132911</t>
+          <t>95261; 131698</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>77170; 99799</t>
+          <t>85953; 110952</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>279719; 323479</t>
+          <t>282199; 324901</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>333912; 379041</t>
+          <t>332695; 380370</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>339461; 388587</t>
+          <t>337018; 385979</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>234072; 269132</t>
+          <t>257370; 296780</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>418379</t>
+          <t>457699</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>436084</t>
+          <t>257619</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>854463</t>
+          <t>715317</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>638499; 672924</t>
+          <t>639437; 672786</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>637078; 692109</t>
+          <t>637702; 690614</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>726361; 774060</t>
+          <t>730260; 775679</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>395485; 444252</t>
+          <t>430253; 485431</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>201156; 247086</t>
+          <t>202254; 249874</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>239895; 295315</t>
+          <t>241307; 294932</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>288316; 346981</t>
+          <t>288692; 346949</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>286160; 674187</t>
+          <t>238666; 279168</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>847160; 914828</t>
+          <t>850179; 919693</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>887821; 971263</t>
+          <t>888787; 971285</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1028731; 1105522</t>
+          <t>1033720; 1108884</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>725456; 1152980</t>
+          <t>683385; 748748</t>
         </is>
       </c>
     </row>
